--- a/ESP32_pin_mapping.xlsx
+++ b/ESP32_pin_mapping.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/46ff64822b9a43f4/Main/projects/V67_cycletron/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/46ff64822b9a43f4/Main/projects/ESP32-DevBoard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{5D9F6ADD-5572-4F2F-AC6E-C266B563B89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3578758E-66FD-4479-B38C-2DE2A1D2B851}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{5D9F6ADD-5572-4F2F-AC6E-C266B563B89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C07B06DD-ABDC-4742-91F9-00DC96E04D98}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6F177B62-EEB3-4EA4-922A-B73648E8DE5C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6F177B62-EEB3-4EA4-922A-B73648E8DE5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="219">
   <si>
     <t xml:space="preserve"> I04  </t>
   </si>
@@ -363,6 +364,339 @@
   </si>
   <si>
     <t>ADC1_CH1</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>U1RXD</t>
+  </si>
+  <si>
+    <t>U1TXD</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>1,40</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>EPAD</t>
+  </si>
+  <si>
+    <t>3V3</t>
+  </si>
+  <si>
+    <t>Power supply</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>High: on, enables the chip. Low: off, the chip powers off. Note: Do not leave the EN pin floating.</t>
+  </si>
+  <si>
+    <t>GPIO0</t>
+  </si>
+  <si>
+    <t>J3-14</t>
+  </si>
+  <si>
+    <t>3.3V</t>
+  </si>
+  <si>
+    <t>I/O/T</t>
+  </si>
+  <si>
+    <t>J3-4</t>
+  </si>
+  <si>
+    <t>0.0V</t>
+  </si>
+  <si>
+    <t>J3-5</t>
+  </si>
+  <si>
+    <t>GPIO3</t>
+  </si>
+  <si>
+    <t>J1-13</t>
+  </si>
+  <si>
+    <t>GPIO4</t>
+  </si>
+  <si>
+    <t>J1-4</t>
+  </si>
+  <si>
+    <t>GPIO5</t>
+  </si>
+  <si>
+    <t>J1-5</t>
+  </si>
+  <si>
+    <t>GPIO6</t>
+  </si>
+  <si>
+    <t>J1-6</t>
+  </si>
+  <si>
+    <t>GPIO7</t>
+  </si>
+  <si>
+    <t>J1-7</t>
+  </si>
+  <si>
+    <t>GPIO8</t>
+  </si>
+  <si>
+    <t>J1-12</t>
+  </si>
+  <si>
+    <t>GPIO9</t>
+  </si>
+  <si>
+    <t>J1-15</t>
+  </si>
+  <si>
+    <t>GPIO10</t>
+  </si>
+  <si>
+    <t>J1-16</t>
+  </si>
+  <si>
+    <t>GPIO11</t>
+  </si>
+  <si>
+    <t>J1-17</t>
+  </si>
+  <si>
+    <t>GPIO12</t>
+  </si>
+  <si>
+    <t>J1-18</t>
+  </si>
+  <si>
+    <t>J1-19</t>
+  </si>
+  <si>
+    <t>J1-20</t>
+  </si>
+  <si>
+    <t>GPIO15</t>
+  </si>
+  <si>
+    <t>J1-8</t>
+  </si>
+  <si>
+    <t>GPIO16</t>
+  </si>
+  <si>
+    <t>J1-9</t>
+  </si>
+  <si>
+    <t>GPIO17</t>
+  </si>
+  <si>
+    <t>J1-10</t>
+  </si>
+  <si>
+    <t>GPIO18</t>
+  </si>
+  <si>
+    <t>J1-11</t>
+  </si>
+  <si>
+    <t>USB_D-</t>
+  </si>
+  <si>
+    <t>J3-20</t>
+  </si>
+  <si>
+    <t>USB_D+</t>
+  </si>
+  <si>
+    <t>J3-19</t>
+  </si>
+  <si>
+    <t>J3-18</t>
+  </si>
+  <si>
+    <t>J3-13</t>
+  </si>
+  <si>
+    <t>J3-12</t>
+  </si>
+  <si>
+    <t>J3-11</t>
+  </si>
+  <si>
+    <t>J3-10</t>
+  </si>
+  <si>
+    <t>MTCK</t>
+  </si>
+  <si>
+    <t>J3-9</t>
+  </si>
+  <si>
+    <t>MTDO</t>
+  </si>
+  <si>
+    <t>J3-8</t>
+  </si>
+  <si>
+    <t>MTDI</t>
+  </si>
+  <si>
+    <t>J3-7</t>
+  </si>
+  <si>
+    <t>MTMS</t>
+  </si>
+  <si>
+    <t>J3-6</t>
+  </si>
+  <si>
+    <t>U0TXD</t>
+  </si>
+  <si>
+    <t>J3-2</t>
+  </si>
+  <si>
+    <t>U0RXD</t>
+  </si>
+  <si>
+    <t>J3-3</t>
+  </si>
+  <si>
+    <t>J3-15</t>
+  </si>
+  <si>
+    <t>GPIO46</t>
+  </si>
+  <si>
+    <t>J1-14</t>
+  </si>
+  <si>
+    <t>J3-17</t>
+  </si>
+  <si>
+    <t>0.0V *3.3V</t>
+  </si>
+  <si>
+    <t>J3-16</t>
+  </si>
+  <si>
+    <t>Additional notes</t>
+  </si>
+  <si>
+    <t>RTC_GPIO0, GPIO0</t>
+  </si>
+  <si>
+    <t>RTC_GPIO1, GPIO1, TOUCH1, ADC1_CH0</t>
+  </si>
+  <si>
+    <t>RTC_GPIO2, GPIO2, TOUCH2, ADC1_CH1</t>
+  </si>
+  <si>
+    <t>RTC_GPIO3, GPIO3, TOUCH3, ADC1_CH2</t>
+  </si>
+  <si>
+    <t>RTC_GPIO4, GPIO4, TOUCH4, ADC1_CH3</t>
+  </si>
+  <si>
+    <t>RTC_GPIO5, GPIO5, TOUCH5, ADC1_CH4</t>
+  </si>
+  <si>
+    <t>RTC_GPIO6, GPIO6, TOUCH6, ADC1_CH5</t>
+  </si>
+  <si>
+    <t>RTC_GPIO7, GPIO7, TOUCH7, ADC1_CH6</t>
+  </si>
+  <si>
+    <t>RTC_GPIO8, GPIO8, TOUCH8, ADC1_CH7, SUBSPICS1</t>
+  </si>
+  <si>
+    <t>RTC_GPIO9, GPIO9, TOUCH9, ADC1_CH8, FSPIHD, SUBSPIHD</t>
+  </si>
+  <si>
+    <t>RTC_GPIO10, GPIO10, TOUCH10, ADC1_CH9, FSPICS0, FSPIIO4, SUBSPICS0</t>
+  </si>
+  <si>
+    <t>RTC_GPIO11, GPIO11, TOUCH11, ADC2_CH0, FSPID, FSPIIO5, SUBSPID</t>
+  </si>
+  <si>
+    <t>RTC_GPIO12, GPIO12, TOUCH12, ADC2_CH1, FSPICLK, FSPIIO6, SUBSPICLK</t>
+  </si>
+  <si>
+    <t>RTC_GPIO13, GPIO13, TOUCH13, ADC2_CH2, FSPIQ, FSPIIO7, SUBSPIQ</t>
+  </si>
+  <si>
+    <t>RTC_GPIO14, GPIO14, TOUCH14, ADC2_CH3, FSPIWP, FSPIDQS, SUBSPIWP</t>
+  </si>
+  <si>
+    <t>RTC_GPIO15, GPIO15, U0RTS, ADC2_CH4, XTAL_32K_P</t>
+  </si>
+  <si>
+    <t>RTC_GPIO16, GPIO16, U0CTS, ADC2_CH5, XTAL_32K_N</t>
+  </si>
+  <si>
+    <t>RTC_GPIO17, GPIO17, U1TXD, ADC2_CH6</t>
+  </si>
+  <si>
+    <t>RTC_GPIO18, GPIO18, U1RXD, ADC2_CH7, CLK_OUT3</t>
+  </si>
+  <si>
+    <t>RTC_GPIO19, GPIO19, U1RTS, ADC2_CH8, CLK_OUT2, USB_D-</t>
+  </si>
+  <si>
+    <t>RTC_GPIO20, GPIO20, U1CTS, ADC2_CH9, CLK_OUT1, USB_D+</t>
+  </si>
+  <si>
+    <t>RTC_GPIO21, GPIO21</t>
+  </si>
+  <si>
+    <t>SPIIO6, GPIO35, FSPID, SUBSPID</t>
+  </si>
+  <si>
+    <t>SPIIO7, GPIO36, FSPICLK, SUBSPICLK</t>
+  </si>
+  <si>
+    <t>SPIDQS, GPIO37, FSPIQ, SUBSPIQ</t>
+  </si>
+  <si>
+    <t>GPIO38, FSPIWP, SUBSPIWP</t>
+  </si>
+  <si>
+    <t>MTCK, GPIO39, CLK_OUT3, SUBSPICS1</t>
+  </si>
+  <si>
+    <t>MTDO, GPIO40, CLK_OUT2</t>
+  </si>
+  <si>
+    <t>MTDI, GPIO41, CLK_OUT1</t>
+  </si>
+  <si>
+    <t>MTMS, GPIO42</t>
+  </si>
+  <si>
+    <t>U0TXD, GPIO43, CLK_OUT1</t>
+  </si>
+  <si>
+    <t>U0RXD, GPIO44, CLK_OUT2</t>
+  </si>
+  <si>
+    <t>SPICLK_P_DIFF, GPIO47, SUBSPICLK_P_DIFF</t>
+  </si>
+  <si>
+    <t>SPICLK_N_DIFF, GPIO48, SUBSPICLK_N_DIFF</t>
   </si>
 </sst>
 </file>
@@ -415,6 +749,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -734,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F569A56D-9C51-4240-955B-A761D3977223}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -744,7 +1082,7 @@
     <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>81</v>
       </c>
@@ -760,8 +1098,11 @@
       <c r="E1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -778,7 +1119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -795,7 +1136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -812,7 +1153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>82</v>
       </c>
@@ -829,7 +1170,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -846,7 +1187,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -863,7 +1204,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -879,8 +1220,11 @@
       <c r="E8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -896,8 +1240,11 @@
       <c r="E9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>82</v>
       </c>
@@ -914,7 +1261,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>82</v>
       </c>
@@ -931,7 +1278,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>82</v>
       </c>
@@ -945,7 +1292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -962,7 +1309,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -979,7 +1326,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -996,7 +1343,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1280,4 +1627,796 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15FCF695-7EF1-4910-9623-33987547923C}">
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" t="s">
+        <v>123</v>
+      </c>
+      <c r="F15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>149</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>152</v>
+      </c>
+      <c r="D21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>154</v>
+      </c>
+      <c r="D22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" t="s">
+        <v>123</v>
+      </c>
+      <c r="F23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" t="s">
+        <v>125</v>
+      </c>
+      <c r="E24" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>159</v>
+      </c>
+      <c r="B25">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>160</v>
+      </c>
+      <c r="D25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F25" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>161</v>
+      </c>
+      <c r="D26" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27">
+        <v>28</v>
+      </c>
+      <c r="C27" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" t="s">
+        <v>123</v>
+      </c>
+      <c r="F28" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B29">
+        <v>30</v>
+      </c>
+      <c r="C29" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" t="s">
+        <v>123</v>
+      </c>
+      <c r="F29" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30">
+        <v>31</v>
+      </c>
+      <c r="C30" t="s">
+        <v>165</v>
+      </c>
+      <c r="D30" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F31" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>168</v>
+      </c>
+      <c r="B32">
+        <v>33</v>
+      </c>
+      <c r="C32" t="s">
+        <v>169</v>
+      </c>
+      <c r="D32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F32" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33">
+        <v>34</v>
+      </c>
+      <c r="C33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34">
+        <v>35</v>
+      </c>
+      <c r="C34" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" t="s">
+        <v>123</v>
+      </c>
+      <c r="F34" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>174</v>
+      </c>
+      <c r="B35">
+        <v>37</v>
+      </c>
+      <c r="C35" t="s">
+        <v>175</v>
+      </c>
+      <c r="D35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" t="s">
+        <v>123</v>
+      </c>
+      <c r="F35" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36">
+        <v>36</v>
+      </c>
+      <c r="C36" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" t="s">
+        <v>122</v>
+      </c>
+      <c r="E36" t="s">
+        <v>123</v>
+      </c>
+      <c r="F36" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>178</v>
+      </c>
+      <c r="D37" t="s">
+        <v>125</v>
+      </c>
+      <c r="E37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>179</v>
+      </c>
+      <c r="B38">
+        <v>16</v>
+      </c>
+      <c r="C38" t="s">
+        <v>180</v>
+      </c>
+      <c r="D38" t="s">
+        <v>125</v>
+      </c>
+      <c r="E38" t="s">
+        <v>123</v>
+      </c>
+      <c r="F38" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39">
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
+        <v>181</v>
+      </c>
+      <c r="D39" t="s">
+        <v>182</v>
+      </c>
+      <c r="E39" t="s">
+        <v>123</v>
+      </c>
+      <c r="F39" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>183</v>
+      </c>
+      <c r="D40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" t="s">
+        <v>123</v>
+      </c>
+      <c r="F40" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>